--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487474_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487474_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2185</v>
+        <v>3.9148</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0938</v>
+        <v>4.7634</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8753</v>
+        <v>-0.8486</v>
       </c>
       <c r="G2" t="n">
         <v>4.0327</v>
@@ -610,13 +610,13 @@
         <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9104</v>
+        <v>0.6068</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1349</v>
+        <v>0.8046</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2245</v>
+        <v>-0.1978</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3329</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>S. RODRÍGUEZ TAPIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1672</v>
+        <v>2.9065</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0089</v>
+        <v>1.498</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1583</v>
+        <v>1.4085</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6325</v>
+        <v>1.4154</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4999</v>
+        <v>-0.1912</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1324</v>
+        <v>1.6066</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1502</v>
+        <v>1.0019</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6177</v>
+        <v>0.3504</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7679</v>
+        <v>0.6515</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4822</v>
+        <v>0.4135</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8822</v>
+        <v>-0.5416</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3645</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.1543</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9377</v>
+        <v>-1.3709</v>
       </c>
       <c r="R3" t="n">
         <v>0.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>4.0232</v>
+        <v>0.8621</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7964</v>
+        <v>0.6505</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2268</v>
+        <v>0.2116</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6659</v>
+        <v>1.2166</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ TAPIA</t>
+          <t>H. SANCHEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6797</v>
+        <v>2.4458</v>
       </c>
       <c r="E4" t="n">
-        <v>1.191</v>
+        <v>1.504</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4887</v>
+        <v>0.9418</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4154</v>
+        <v>2.6495</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1912</v>
+        <v>0.882</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6066</v>
+        <v>1.7675</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0019</v>
+        <v>2.8391</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3504</v>
+        <v>1.082</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6515</v>
+        <v>1.7571</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4135</v>
+        <v>-0.1896</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5416</v>
+        <v>-0.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.0104</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3709</v>
+        <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6352</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3435</v>
+        <v>-0.0229</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2918</v>
+        <v>-0.0437</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2166</v>
+        <v>-0.3329</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2166</v>
+        <v>-0.3329</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. SANCHEZ EXPOSITO</t>
+          <t>Á. SONEIRA BOO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8005</v>
+        <v>2.3731</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9923</v>
+        <v>1.518</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8082</v>
+        <v>0.8551</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6495</v>
+        <v>2.1476</v>
       </c>
       <c r="H5" t="n">
-        <v>0.882</v>
+        <v>0.7531</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7675</v>
+        <v>1.3945</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8391</v>
+        <v>2.8778</v>
       </c>
       <c r="K5" t="n">
-        <v>1.082</v>
+        <v>0.8166</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7571</v>
+        <v>2.0612</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1896</v>
+        <v>-0.7302</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2</v>
+        <v>-0.0635</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0104</v>
+        <v>-0.6667</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-1.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7119</v>
+        <v>-0.1661</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5346</v>
+        <v>-0.1847</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1773</v>
+        <v>0.0185</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Á. SONEIRA BOO</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6965</v>
+        <v>1.2416</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1087</v>
+        <v>-0.0172</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5878</v>
+        <v>1.2588</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1476</v>
+        <v>4.2996</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7531</v>
+        <v>0.5662</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3945</v>
+        <v>3.7334</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8778</v>
+        <v>4.885</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8166</v>
+        <v>1.036</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0612</v>
+        <v>3.8491</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7302</v>
+        <v>-0.5854</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0635</v>
+        <v>-0.4698</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6667</v>
+        <v>-0.1157</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3917</v>
+        <v>-2.7419</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1751</v>
+        <v>-4.3087</v>
       </c>
       <c r="R6" t="n">
         <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8428</v>
+        <v>0.6827</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.594</v>
+        <v>0.4052</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2488</v>
+        <v>0.2775</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.9988</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.9988</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3126</v>
+        <v>1.1181</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1874</v>
+        <v>0.9905</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1251</v>
+        <v>0.1276</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2996</v>
+        <v>0.5534</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5662</v>
+        <v>-1.8663</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7334</v>
+        <v>2.4197</v>
       </c>
       <c r="J7" t="n">
-        <v>4.885</v>
+        <v>1.2221</v>
       </c>
       <c r="K7" t="n">
-        <v>1.036</v>
+        <v>0.0356</v>
       </c>
       <c r="L7" t="n">
-        <v>3.8491</v>
+        <v>1.1865</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5854</v>
+        <v>-0.6687</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4698</v>
+        <v>-1.9019</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1157</v>
+        <v>1.2332</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.7419</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.3087</v>
+        <v>-1.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7537</v>
+        <v>0.4852</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6099</v>
+        <v>0.6681</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1438</v>
+        <v>-0.1829</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9988</v>
+        <v>0.2754</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9988</v>
+        <v>0.2754</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4402</v>
+        <v>0.9564</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2397</v>
+        <v>0.6491</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2005</v>
+        <v>0.3074</v>
       </c>
       <c r="G8" t="n">
         <v>0.5647</v>
@@ -1078,13 +1078,13 @@
         <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3204</v>
+        <v>0.1958</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1188</v>
+        <v>0.2905</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2016</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. FUENTES PRADO</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2952</v>
+        <v>0.9067</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1326</v>
+        <v>-1.0378</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8374</v>
+        <v>1.9445</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6483</v>
+        <v>0.6325</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2589</v>
+        <v>-1.4999</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3893</v>
+        <v>2.1324</v>
       </c>
       <c r="J9" t="n">
-        <v>2.192</v>
+        <v>0.1502</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9391</v>
+        <v>-0.6177</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2529</v>
+        <v>0.7679</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5437</v>
+        <v>0.4822</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6802</v>
+        <v>-0.8822</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1364</v>
+        <v>1.3645</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1958</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3323</v>
+        <v>1.7626</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0594</v>
+        <v>1.7497</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2729</v>
+        <v>0.0129</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2166</v>
+        <v>0.6659</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2166</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
+          <t>N. FUENTES PRADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1145</v>
+        <v>0.6022</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1352</v>
+        <v>2.4396</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0207</v>
+        <v>-1.8374</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5534</v>
+        <v>1.6483</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8663</v>
+        <v>0.2589</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4197</v>
+        <v>1.3893</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2221</v>
+        <v>2.192</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0356</v>
+        <v>0.9391</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1865</v>
+        <v>1.2529</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6687</v>
+        <v>-0.5437</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9019</v>
+        <v>-0.6802</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2332</v>
+        <v>0.1364</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1958</v>
+        <v>0.1958</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7474</v>
+        <v>-0.0253</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4576</v>
+        <v>0.2476</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2898</v>
+        <v>-0.2729</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2754</v>
+        <v>-1.2166</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2724</v>
+        <v>-0.513</v>
       </c>
       <c r="E11" t="n">
         <v>-0.318</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0456</v>
+        <v>-0.195</v>
       </c>
       <c r="G11" t="n">
         <v>0.647</v>
@@ -1312,13 +1312,13 @@
         <v>0.9792</v>
       </c>
       <c r="S11" t="n">
-        <v>0.493</v>
+        <v>0.2525</v>
       </c>
       <c r="T11" t="n">
         <v>0.0882</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4048</v>
+        <v>0.1642</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2166</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1079</v>
+        <v>-2.4229</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0441</v>
+        <v>-1.2254</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0638</v>
+        <v>-1.1975</v>
       </c>
       <c r="G12" t="n">
         <v>-2.103</v>
@@ -1390,13 +1390,13 @@
         <v>0.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.142</v>
+        <v>0.543</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4576</v>
+        <v>0.3611</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3155</v>
+        <v>0.1819</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2754</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8854</v>
+        <v>-6.2994</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5545</v>
+        <v>-3.8615</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.331</v>
+        <v>-2.4379</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9726</v>
@@ -1468,13 +1468,13 @@
         <v>0.1958</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7715</v>
+        <v>0.3576</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.2147</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2498</v>
+        <v>0.1429</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7673</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.230199999999997</v>
+        <v>7.229899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>6.902600000000001</v>
+        <v>6.902700000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3274000000000004</v>
+        <v>0.3273000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>15.5151</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3697</v>
+        <v>1.369700000000001</v>
       </c>
       <c r="I14" t="n">
         <v>14.1454</v>
@@ -1546,13 +1546,13 @@
         <v>10.7715</v>
       </c>
       <c r="S14" t="n">
-        <v>5.4902</v>
+        <v>5.4903</v>
       </c>
       <c r="T14" t="n">
         <v>5.2726</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2176</v>
+        <v>0.2175000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-3.9826</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0662</v>
+        <v>4.1615</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9474</v>
+        <v>4.31</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1188</v>
+        <v>-0.1485</v>
       </c>
       <c r="G15" t="n">
         <v>1.5492</v>
@@ -1624,13 +1624,13 @@
         <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>2.676</v>
+        <v>0.7713</v>
       </c>
       <c r="T15" t="n">
-        <v>2.212</v>
+        <v>0.5746</v>
       </c>
       <c r="U15" t="n">
-        <v>0.464</v>
+        <v>0.1967</v>
       </c>
       <c r="V15" t="n">
         <v>0.6659</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4282</v>
+        <v>0.1757</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2816</v>
+        <v>-0.9746</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8535</v>
+        <v>1.1503</v>
       </c>
       <c r="G16" t="n">
         <v>-1.4549</v>
@@ -1702,13 +1702,13 @@
         <v>2.3502</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3234</v>
+        <v>-0.7196</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6358</v>
+        <v>-0.3288</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6876</v>
+        <v>-0.3908</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6035</v>
+        <v>-0.5233</v>
       </c>
       <c r="E17" t="n">
         <v>-0.1174</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4861</v>
+        <v>-0.4059</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3423</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2612</v>
+        <v>-0.181</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.083</v>
+        <v>-0.0028</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. SAMA PEREZ</t>
+          <t>H. PALOMARES BARRADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.597</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1117</v>
+        <v>-0.6339</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6358</v>
+        <v>0.0369</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.8658</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4913</v>
+        <v>-1.1174</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3745</v>
+        <v>0.3185</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8934</v>
+        <v>-0.601</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1362</v>
+        <v>-0.6414</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0297</v>
+        <v>0.0404</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.7593</v>
+        <v>-0.1979</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3551</v>
+        <v>-0.476</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.4041</v>
+        <v>0.2781</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9585</v>
+        <v>0.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.917</v>
+        <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1599</v>
+        <v>-0.1898</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9534</v>
+        <v>-0.0329</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7935</v>
+        <v>-0.1569</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. PALOMARES BARRADO</t>
+          <t>A. HERMIDA PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.775</v>
+        <v>-0.6082</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8386</v>
+        <v>-0.505</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0636</v>
+        <v>-0.1033</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-4.4741</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1174</v>
+        <v>-2.2413</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3185</v>
+        <v>-2.2328</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.601</v>
+        <v>-1.4555</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6414</v>
+        <v>-0.8185</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0404</v>
+        <v>-0.637</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1979</v>
+        <v>-3.0187</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.476</v>
+        <v>-1.4228</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2781</v>
+        <v>-1.5958</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3917</v>
+        <v>3.1336</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3917</v>
+        <v>4.1128</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3678</v>
+        <v>-1.3104</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2376</v>
+        <v>-0.1129</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1302</v>
+        <v>-1.1974</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.0427</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.0427</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ ZAS</t>
+          <t>P. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6235</v>
+        <v>-0.9325</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9347</v>
+        <v>0.2061</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6888</v>
+        <v>-1.1386</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5231</v>
+        <v>-1.1006</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0987</v>
+        <v>1.6376</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6218</v>
+        <v>-2.7382</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5189</v>
+        <v>3.4023</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1633</v>
+        <v>3.4687</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6822</v>
+        <v>-0.0664</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0041</v>
+        <v>-4.503</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0646</v>
+        <v>-1.8311</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9396</v>
+        <v>-2.6718</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7834</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.917</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7834</v>
+        <v>3.917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8838</v>
+        <v>-1.3814</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4158</v>
+        <v>-0.4958</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.468</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.5495</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ GONZALEZ</t>
+          <t>I. SAMA PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8655</v>
+        <v>-1.332</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5102</v>
+        <v>-0.7257</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3553</v>
+        <v>-0.6063</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1006</v>
+        <v>-2.8658</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6376</v>
+        <v>-1.4913</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7382</v>
+        <v>-1.3745</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4023</v>
+        <v>0.8934</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4687</v>
+        <v>-0.1362</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0664</v>
+        <v>1.0297</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.503</v>
+        <v>-3.7593</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8311</v>
+        <v>-1.3551</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.6718</v>
+        <v>-2.4041</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.9585</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R21" t="n">
         <v>3.917</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.3144</v>
+        <v>-0.4246</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2122</v>
+        <v>0.3393</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1022</v>
+        <v>-0.764</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5495</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. HERMIDA PEREZ</t>
+          <t>M. FERNANDEZ ZAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0934</v>
+        <v>-1.4769</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.426</v>
+        <v>-0.6277</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6674</v>
+        <v>-0.8492</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.4741</v>
+        <v>-1.5231</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2413</v>
+        <v>0.0987</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2328</v>
+        <v>-1.6218</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4555</v>
+        <v>-0.5189</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8185</v>
+        <v>0.1633</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.637</v>
+        <v>-0.6822</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.0187</v>
+        <v>-1.0041</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4228</v>
+        <v>-0.0646</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5958</v>
+        <v>-0.9396</v>
       </c>
       <c r="P22" t="n">
-        <v>3.1336</v>
+        <v>0.7834</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4.1128</v>
+        <v>0.7834</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.7955</v>
+        <v>-0.7372</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0339</v>
+        <v>-0.1088</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.7616</v>
+        <v>-0.6284</v>
       </c>
       <c r="V22" t="n">
-        <v>2.0427</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.0427</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.536</v>
+        <v>-2.3535</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6813</v>
+        <v>-0.579</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8547</v>
+        <v>-1.7745</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3135</v>
@@ -2248,13 +2248,13 @@
         <v>0.5875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5935</v>
+        <v>-0.411</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1012</v>
+        <v>0.0012</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4923</v>
+        <v>-0.4121</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2166</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6237</v>
+        <v>-3.017</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3732</v>
+        <v>-0.6802</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2505</v>
+        <v>-2.3368</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1909</v>
@@ -2326,13 +2326,13 @@
         <v>2.3502</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2135</v>
+        <v>-0.1798</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4317</v>
+        <v>0.1247</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2182</v>
+        <v>-0.3045</v>
       </c>
       <c r="V24" t="n">
         <v>0.9412</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.2301</v>
+        <v>-6.5032</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3272999999999997</v>
+        <v>-0.3274000000000007</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.902699999999999</v>
+        <v>-6.1759</v>
       </c>
       <c r="G25" t="n">
         <v>-15.5149</v>
@@ -2380,7 +2380,7 @@
         <v>5.635199999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>7.7858</v>
+        <v>7.785799999999998</v>
       </c>
       <c r="L25" t="n">
         <v>-2.1505</v>
@@ -2404,13 +2404,13 @@
         <v>20.5641</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.490199999999999</v>
+        <v>-4.7635</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2176000000000002</v>
+        <v>-0.2176</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.272600000000002</v>
+        <v>-4.5458</v>
       </c>
       <c r="V25" t="n">
         <v>3.9827</v>
